--- a/data/doctor_added_interactions.xlsx
+++ b/data/doctor_added_interactions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,28 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>Interaction Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-03 17:38:14</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ibuprofen</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Test interaction from advanced pipeline</t>
         </is>
       </c>
     </row>

--- a/data/doctor_added_interactions.xlsx
+++ b/data/doctor_added_interactions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,50 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>Test interaction from advanced pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:11:30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ibuprofen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prednisone</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Increased gastrointestinal bleeding and ulcer risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:12:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ibuprofen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prednisone</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Increased gastrointestinal bleeding and ulcer risk.</t>
         </is>
       </c>
     </row>
